--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4960-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4960-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2582A81D-25B4-4A90-8A77-CDE7B96B01C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D4385F8-A461-4BB7-B560-71B337EE1F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{CFBF23CF-A2CE-4F8A-8754-CBC1EE7B8AF8}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{C9D10DCC-61F1-42B2-919A-B9648C20E7A2}"/>
   </bookViews>
   <sheets>
     <sheet name="4960-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1457,20 +1457,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E5CB2CF-D9EF-4F84-A4C6-50589F77E114}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC24469-68C5-4420-B018-1BBD02248968}">
   <dimension ref="A1:R33"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.21875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1498,7 +1498,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1528,7 +1528,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1624,7 +1624,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2023</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>26</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2022</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2021</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2020</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2019</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2018</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2017</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2016</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2015</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2014</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2013</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2012</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2011</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37" t="s">
         <v>38</v>
       </c>
